--- a/models/sovereigns/Rwanda_Sovereign_Model.xlsx
+++ b/models/sovereigns/Rwanda_Sovereign_Model.xlsx
@@ -929,16 +929,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>5.909</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1098,16 +1116,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>17.336</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Rwanda_Sovereign_Model.xlsx
+++ b/models/sovereigns/Rwanda_Sovereign_Model.xlsx
@@ -652,12 +652,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BNR</t>
+          <t>Gemini position citing BNR MPC statement (reported, unverified, no URL)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -700,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BNR / NISR</t>
+          <t>Gemini position citing BNR/NISR (reported, unverified, no URL)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -726,17 +726,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>H1 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fitch</t>
+          <t>Gemini position citing NISR (reported, unverified, no URL)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11-Sep-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -826,17 +826,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>FY2025/26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>Gemini position attributing to IMF release (reported, unverified, no URL)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BNR / Fitch</t>
+          <t>Gemini position citing Fitch (reported, near 15% deficit, unverified, no URL)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11-Sep-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -974,22 +974,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BNR</t>
+          <t>Gemini position (reported, unverified, no URL)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross reserves</t>
+          <t>not stated (reported ~US$2.2bn)</t>
         </is>
       </c>
     </row>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BNR</t>
+          <t>Gemini position (reported ~4.0 months of imports, unverified, no URL)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MINECOFIN</t>
+          <t>Claude and Gemini positions recalling US$620m 5.50% due Aug-31 (prospectus not retrieved)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15-May-26</t>
+          <t>May-26</t>
         </is>
       </c>
     </row>
@@ -1323,25 +1323,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>38-month ECF ($35.7m SDR 26.43m review)</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.319</v>
+          <t>ECF (38-month, reported)</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>Jun-26 (reported)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dec-26</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>moderate</t>
+          <t>Board Dec-26 (reported; first review staff-level agreement 06-Oct-26, SDR 26.43m)</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1385,6 +1377,16 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2027F</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1398,7 +1400,9 @@
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1411,9 +1415,13 @@
       <c r="D3" s="2" t="n">
         <v>7.8</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fitch, 11-Sep-26</t>
+      <c r="E3" s="2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fitch forecast via Gemini position (unverified), 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1434,9 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1439,9 +1449,11 @@
       <c r="D5" s="2" t="n">
         <v>-15</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>BNR / Fitch, 11-Sep-26</t>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gemini position citing Fitch (unverified), 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1454,13 +1466,19 @@
       <c r="B6" s="2" t="n">
         <v>-4.8</v>
       </c>
-      <c r="C6" s="2" t="n"/>
+      <c r="C6" s="2" t="n">
+        <v>-4.8</v>
+      </c>
       <c r="D6" s="2" t="n">
         <v>-4.5</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>IMF / Fitch, 06-Oct-26</t>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Gemini position citing IMF (FY2025/26) and Fitch (FY2026/27), unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1491,9 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1486,7 +1506,9 @@
       <c r="D8" s="2" t="n">
         <v>77.5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Fitch, 11-Sep-26</t>
         </is>
@@ -1503,7 +1525,9 @@
       <c r="D9" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Fitch, 11-Sep-26</t>
         </is>
@@ -1519,10 +1543,14 @@
       <c r="C10" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>BNR, 31-Aug-26</t>
+      <c r="D10" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Gemini position (unverified), 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1563,9 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1546,7 +1576,9 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Rwanda_Sovereign_Model.xlsx
+++ b/models/sovereigns/Rwanda_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/rwanda.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/rwanda.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Rwanda_Sovereign_Model.xlsx
+++ b/models/sovereigns/Rwanda_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gemini position citing BNR MPC statement (reported, unverified, no URL)</t>
+          <t>BNR MPC statement via Gemini position (reported, no URL, unverified)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gemini position citing BNR/NISR (reported, unverified, no URL)</t>
+          <t>BNR/NISR via Gemini position (reported, no URL, unverified)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>H1 2026</t>
+          <t>H1-26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gemini position citing NISR (reported, unverified, no URL)</t>
+          <t>NISR via Gemini position (reported, no URL, unverified)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gemini position attributing to IMF release (reported, unverified, no URL)</t>
+          <t>IMF release via Gemini position (reported, no URL, unverified)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gemini position citing Fitch (reported, near 15% deficit, unverified, no URL)</t>
+          <t>Gemini position, 'near 15% of GDP' deficit (reported, no URL, unverified)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gemini position (reported, unverified, no URL)</t>
+          <t>Gemini position (reported, no URL, unverified)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gemini position (reported ~4.0 months of imports, unverified, no URL)</t>
+          <t>Gemini position (reported ~4.0 months, no URL, unverified)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Aug-21 issue, 5.50% due 2031</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Claude and Gemini positions recalling US$620m 5.50% due Aug-31 (prospectus not retrieved)</t>
+          <t>Recalled by both models; prospectus not retrieved (Medium confidence)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ECF (38-month, reported)</t>
+          <t>ECF, 38-month (reported by Gemini, unverified)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Jun-26 (reported)</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Board Dec-26 (reported; first review staff-level agreement 06-Oct-26, SDR 26.43m)</t>
+          <t>Board date Dec-26 (first-review staff-level agreement 06-Oct-26, SDR 26.43m)</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fitch forecast via Gemini position (unverified), 08-Oct-26</t>
+          <t>2026E is Fitch forecast via Gemini position, no URL, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gemini position citing Fitch (unverified), 08-Oct-26</t>
+          <t>Gemini position, reported near -15% for 2026, no URL, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gemini position (unverified), 08-Oct-26</t>
+          <t>Gemini position, reported ~US$2.2bn, definition not stated, no URL, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Rwanda_Sovereign_Model.xlsx
+++ b/models/sovereigns/Rwanda_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BNR MPC statement via Gemini position (reported, no URL, unverified)</t>
+          <t>BNR MPC statement as reported by Gemini position, no URL, unverified</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BNR/NISR via Gemini position (reported, no URL, unverified)</t>
+          <t>BNR/NISR as reported by Gemini position, no URL, unverified</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>H1-26</t>
+          <t>H1 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NISR via Gemini position (reported, no URL, unverified)</t>
+          <t>NISR as reported by Gemini position, no URL, unverified</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF release via Gemini position (reported, no URL, unverified)</t>
+          <t>IMF release as reported by Gemini position, no URL, unverified; fiscal-year convention not stated</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gemini position, 'near 15% of GDP' deficit (reported, no URL, unverified)</t>
+          <t>Reported near 15% of GDP deficit (Gemini position, no URL, unverified)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gemini position (reported, no URL, unverified)</t>
+          <t>Reported by Gemini position, no URL, unverified</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>not stated (reported ~US$2.2bn)</t>
+          <t>definition not stated (reported ~US$2.2bn)</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gemini position (reported ~4.0 months, no URL, unverified)</t>
+          <t>Reported by Gemini position, no URL, unverified</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Aug-21 issue, 5.50% due 2031</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recalled by both models; prospectus not retrieved (Medium confidence)</t>
+          <t>US$620m 5.50% bond issued Aug-21, recalled by both models, prospectus not retrieved</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ECF, 38-month (reported by Gemini, unverified)</t>
+          <t>38-month ECF (reported; first-review staff-level agreement 06-Oct-26 for SDR 26.43m)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Board date Dec-26 (first-review staff-level agreement 06-Oct-26, SDR 26.43m)</t>
+          <t>Board date Dec-26 (reported)</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026E is Fitch forecast via Gemini position, no URL, unverified, 08-Oct-26</t>
+          <t>Fitch 2026 forecast as reported by Gemini position, no URL, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gemini position, reported near -15% for 2026, no URL, unverified, 08-Oct-26</t>
+          <t>Reported by Gemini position, no URL, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gemini position, reported ~US$2.2bn, definition not stated, no URL, unverified, 08-Oct-26</t>
+          <t>Reported by Gemini position, no URL, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Rwanda_Sovereign_Model.xlsx
+++ b/models/sovereigns/Rwanda_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BNR MPC statement as reported by Gemini position, no URL, unverified</t>
+          <t>BNR MPC statement as reported by Gemini in the adjudicated document, no URL, unverified (Low-Medium)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BNR/NISR as reported by Gemini position, no URL, unverified</t>
+          <t>BNR/NISR as reported by Gemini in the adjudicated document, no URL, unverified (Low-Medium)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NISR as reported by Gemini position, no URL, unverified</t>
+          <t>NISR as reported by Gemini in the adjudicated document, no URL, unverified (Low-Medium)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FY2025/26</t>
+          <t>FY2025/26 (fiscal-year convention not stated)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF release as reported by Gemini position, no URL, unverified; fiscal-year convention not stated</t>
+          <t>IMF release as reported by Gemini via adjudicated document, no URL, unverified (Low)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Reported near 15% of GDP deficit (Gemini position, no URL, unverified)</t>
+          <t>Reported 'near 15% of GDP' deficit, Gemini via adjudicated document, no URL, unverified (Low-Medium)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Reported by Gemini position, no URL, unverified</t>
+          <t>Gemini via adjudicated document, no URL, unverified (Low-Medium)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>definition not stated (reported ~US$2.2bn)</t>
+          <t>not stated in source (reported ~US$2.2bn)</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Reported by Gemini position, no URL, unverified</t>
+          <t>Gemini via adjudicated document, no URL, unverified (Low-Medium)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Aug-21 issue, outstanding</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>US$620m 5.50% bond issued Aug-21, recalled by both models, prospectus not retrieved</t>
+          <t>Recalled by both models (US$620m 5.50% due Aug-31); prospectus not retrieved (Medium)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>38-month ECF (reported; first-review staff-level agreement 06-Oct-26 for SDR 26.43m)</t>
+          <t>38-month ECF (reported)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Board date Dec-26 (reported)</t>
+          <t>Board date Dec-26 following first-review staff-level agreement of 06-Oct-26 (SDR 26.43m disbursement)</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fitch 2026 forecast as reported by Gemini position, no URL, unverified, 08-Oct-26</t>
+          <t>Fitch 2026 forecast as reported by Gemini via adjudicated document, no URL, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Rwanda_Sovereign_Model.xlsx
+++ b/models/sovereigns/Rwanda_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BNR MPC statement as reported by Gemini in the adjudicated document, no URL, unverified (Low-Medium)</t>
+          <t>BNR MPC statement as reported by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BNR/NISR as reported by Gemini in the adjudicated document, no URL, unverified (Low-Medium)</t>
+          <t>NISR/BNR as reported by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NISR as reported by Gemini in the adjudicated document, no URL, unverified (Low-Medium)</t>
+          <t>NISR as reported by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FY2025/26 (fiscal-year convention not stated)</t>
+          <t>FY2025/26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF release as reported by Gemini via adjudicated document, no URL, unverified (Low)</t>
+          <t>IMF release as reported by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Reported 'near 15% of GDP' deficit, Gemini via adjudicated document, no URL, unverified (Low-Medium)</t>
+          <t>Reported near 15% of GDP deficit, Gemini position in run 2026-10-08_1853; unverified, no URL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gemini via adjudicated document, no URL, unverified (Low-Medium)</t>
+          <t>Reported by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>not stated in source (reported ~US$2.2bn)</t>
+          <t>not stated in source (approximate, ~US$2.2bn)</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gemini via adjudicated document, no URL, unverified (Low-Medium)</t>
+          <t>Reported (~4.0 months of imports) by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Aug-21 issue, outstanding</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recalled by both models (US$620m 5.50% due Aug-31); prospectus not retrieved (Medium)</t>
+          <t>US$620m 5.50% bond due Aug-31, recalled by both models; prospectus not retrieved (run 2026-10-08_1853)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>38-month ECF (reported)</t>
+          <t>ECF, 38-month (reported, unverified); first-review staff-level agreement 06-Oct-26, SDR 26.43m</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Board date Dec-26 following first-review staff-level agreement of 06-Oct-26 (SDR 26.43m disbursement)</t>
+          <t>Board date Dec-26 (reported)</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fitch 2026 forecast as reported by Gemini via adjudicated document, no URL, unverified, 08-Oct-26</t>
+          <t>Fitch 2026 forecast as reported by Gemini position, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Reported by Gemini position, no URL, unverified, 08-Oct-26</t>
+          <t>Reported near 15% of GDP deficit, Gemini position, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Rwanda_Sovereign_Model.xlsx
+++ b/models/sovereigns/Rwanda_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BNR MPC statement as reported by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
+          <t>BNR MPC statement as reported by Gemini in adjudicated document, unverified, no URL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NISR/BNR as reported by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
+          <t>BNR/NISR as reported by Gemini in adjudicated document, unverified, no URL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NISR as reported by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
+          <t>NISR as reported by Gemini in adjudicated document, unverified, no URL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF release as reported by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
+          <t>IMF release as reported by Gemini in adjudicated document, unverified, no URL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Reported near 15% of GDP deficit, Gemini position in run 2026-10-08_1853; unverified, no URL</t>
+          <t>Reported near 15% of GDP deficit, Gemini in adjudicated document, unverified, no URL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Reported by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
+          <t>Gemini in adjudicated document, unverified, no URL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>not stated in source (approximate, ~US$2.2bn)</t>
+          <t>Definition not stated (reported ~US$2.2bn)</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Reported (~4.0 months of imports) by Gemini position in run 2026-10-08_1853; unverified, no URL</t>
+          <t>Gemini in adjudicated document, unverified, no URL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fitch</t>
+          <t>Fitch as reported by Gemini in adjudicated document, no URL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>net external debt % GDP</t>
+          <t>Net external debt to GDP as attributed to Fitch by Gemini; unverified (Low)</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Aug-21 issue, outstanding</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>US$620m 5.50% bond due Aug-31, recalled by both models; prospectus not retrieved (run 2026-10-08_1853)</t>
+          <t>Claude and Gemini recall of terms (US$620m 5.50% due Aug-31); prospectus not retrieved, Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ECF, 38-month (reported, unverified); first-review staff-level agreement 06-Oct-26, SDR 26.43m</t>
+          <t>ECF, 38-month (reported, unverified)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>Jun-26 (reported)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Board date Dec-26 (reported)</t>
+          <t>First review: staff-level agreement 06-Oct-26 (SDR 26.43m, ~US$35.7m); Board date Dec-26 (reported)</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fitch 2026 forecast as reported by Gemini position, unverified, 08-Oct-26</t>
+          <t>Fitch 2026 forecast as reported by Gemini, no URL, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Reported near 15% of GDP deficit, Gemini position, unverified, 08-Oct-26</t>
+          <t>Gemini as reported, no URL, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Reported by Gemini position, no URL, unverified, 08-Oct-26</t>
+          <t>Gemini as reported, no URL, unverified, 08-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Rwanda_Sovereign_Model.xlsx
+++ b/models/sovereigns/Rwanda_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/rwanda.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/rwanda.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Rwanda_Sovereign_Model.xlsx
+++ b/models/sovereigns/Rwanda_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/rwanda.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/rwanda.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Rwanda_Sovereign_Model.xlsx
+++ b/models/sovereigns/Rwanda_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/rwanda.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/rwanda.json</t>
         </is>
       </c>
     </row>
